--- a/data/trans_orig/IP2905_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP2905_2023-Provincia-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31799</t>
+          <t>32450</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48979</t>
+          <t>49626</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38794</t>
+          <t>37717</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53824</t>
+          <t>53220</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75376</t>
+          <t>73995</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97487</t>
+          <t>98493</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>67,46%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22421</t>
+          <t>21774</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39601</t>
+          <t>38950</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20783</t>
+          <t>21387</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35813</t>
+          <t>36890</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48520</t>
+          <t>47514</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70631</t>
+          <t>72012</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15832</t>
+          <t>16076</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20102</t>
+          <t>18627</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41852</t>
+          <t>40179</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38958</t>
+          <t>39466</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65884</t>
+          <t>64552</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,24%</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>81274</t>
+          <t>81030</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>81818</t>
+          <t>83491</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>103568</t>
+          <t>105043</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>154892</t>
+          <t>156224</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>181818</t>
+          <t>181310</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,12%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>27287</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38986</t>
+          <t>39026</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31859</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45233</t>
+          <t>44925</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63855</t>
+          <t>64076</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80714</t>
+          <t>80962</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,5%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17013</t>
+          <t>16973</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28289</t>
+          <t>28712</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18721</t>
+          <t>19029</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32095</t>
+          <t>32288</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39238</t>
+          <t>38990</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56097</t>
+          <t>55876</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,58%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20037</t>
+          <t>19990</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34395</t>
+          <t>33517</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21466</t>
+          <t>22182</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49494</t>
+          <t>50791</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>46191</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>78883</t>
+          <t>80724</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>56,99%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33392</t>
+          <t>34270</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47750</t>
+          <t>47797</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24375</t>
+          <t>23078</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52403</t>
+          <t>51687</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62774</t>
+          <t>60933</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94726</t>
+          <t>95466</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>67,39%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15939</t>
+          <t>15961</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23949</t>
+          <t>24499</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18468</t>
+          <t>18385</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28376</t>
+          <t>28195</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37081</t>
+          <t>37245</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49852</t>
+          <t>49838</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,52%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10251</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18261</t>
+          <t>18239</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12343</t>
+          <t>12524</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22251</t>
+          <t>22334</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25067</t>
+          <t>25081</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37838</t>
+          <t>37674</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,29%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29246</t>
+          <t>28951</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37213</t>
+          <t>37150</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38454</t>
+          <t>37731</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48799</t>
+          <t>48760</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>71483</t>
+          <t>70971</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>84117</t>
+          <t>83859</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>86,84%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5576</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13543</t>
+          <t>13838</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>5022</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15328</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>12712</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25088</t>
+          <t>25600</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65943</t>
+          <t>65693</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>85103</t>
+          <t>84725</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>84163</t>
+          <t>83557</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>110728</t>
+          <t>110594</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>157806</t>
+          <t>156429</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>188739</t>
+          <t>189046</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,4%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>36712</t>
+          <t>37090</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>55872</t>
+          <t>56122</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>43852</t>
+          <t>43986</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>70417</t>
+          <t>71023</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>87656</t>
+          <t>87349</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>118589</t>
+          <t>119966</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>43,4%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>44867</t>
+          <t>45587</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>64113</t>
+          <t>64261</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>51424</t>
+          <t>51726</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>73708</t>
+          <t>73541</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>103332</t>
+          <t>103534</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>130859</t>
+          <t>132392</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>47,06%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>63355</t>
+          <t>63207</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>82601</t>
+          <t>81881</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>80156</t>
+          <t>80323</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>102440</t>
+          <t>102138</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>150473</t>
+          <t>148940</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>178000</t>
+          <t>177798</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,2%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>284750</t>
+          <t>286377</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>328568</t>
+          <t>329456</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>347770</t>
+          <t>348861</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>404953</t>
+          <t>404445</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>648831</t>
+          <t>646341</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>719338</t>
+          <t>719224</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,98%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>289997</t>
+          <t>289109</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>333815</t>
+          <t>332188</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>334091</t>
+          <t>334599</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>391274</t>
+          <t>390183</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>638271</t>
+          <t>638385</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>708778</t>
+          <t>711268</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>52,39%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2905_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP2905_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>35901</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29710</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>42317</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>59,57%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>49,3%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>70,22%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>40665</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>32450</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>49626</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>56,95%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>45,45%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>69,5%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>46293</t>
+          <t>27142</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37717</t>
+          <t>21931</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53220</t>
+          <t>33031</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>86958</t>
+          <t>63044</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73995</t>
+          <t>54729</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98493</t>
+          <t>71929</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>62,45%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24362</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>17946</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>30553</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>40,43%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>29,78%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>50,7%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>30735</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>21774</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>38950</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>43,05%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>30,5%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>54,55%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28314</t>
+          <t>27780</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21387</t>
+          <t>21891</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36890</t>
+          <t>32991</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>59049</t>
+          <t>52142</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47514</t>
+          <t>43257</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72012</t>
+          <t>60457</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>52,49%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>26501</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18133</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>37738</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>23,57%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16,13%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>33,57%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>22610</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>16076</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>30184</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>23,28%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>23150</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>15724</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>30425</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>24,38%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>16,56%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>31,08%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>28429</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>18627</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>40179</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>22,99%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>15,06%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>51039</t>
+          <t>49652</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39466</t>
+          <t>38819</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64552</t>
+          <t>65042</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -1176,74 +1176,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>85922</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>74685</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>94290</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>76,43%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>66,43%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>83,87%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>74496</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>66922</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>81030</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>76,72%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>68,92%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>71808</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>64533</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>79234</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>75,62%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>67,96%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>83,44%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>95241</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>83491</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>105043</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>77,01%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>67,51%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>84,94%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>224</t>
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>169737</t>
+          <t>157730</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>156224</t>
+          <t>142340</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>181310</t>
+          <t>168563</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,28%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>112423</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>112423</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112423</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>97106</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>97106</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>97106</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>123670</t>
+          <t>94958</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>123670</t>
+          <t>94958</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>123670</t>
+          <t>94958</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>220776</t>
+          <t>207382</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>220776</t>
+          <t>207382</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>220776</t>
+          <t>207382</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>34154</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>28876</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>40072</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>60,26%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>50,95%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>70,7%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>33608</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>27287</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>39026</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>60,01%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>48,73%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>69,69%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38608</t>
+          <t>33024</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>27354</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44925</t>
+          <t>38418</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>72215</t>
+          <t>67178</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64076</t>
+          <t>59222</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80962</t>
+          <t>75119</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,54%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>22522</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16604</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>27800</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>39,74%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>29,3%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>49,05%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>22391</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>16973</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>28712</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>39,99%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>30,31%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>51,27%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25346</t>
+          <t>21514</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19029</t>
+          <t>16120</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32288</t>
+          <t>27184</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>47737</t>
+          <t>44036</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38990</t>
+          <t>36095</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>55876</t>
+          <t>51992</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,75%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56676</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56676</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>56676</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>55999</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>55999</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55999</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63954</t>
+          <t>54538</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63954</t>
+          <t>54538</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63954</t>
+          <t>54538</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>119952</t>
+          <t>111214</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>119952</t>
+          <t>111214</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>119952</t>
+          <t>111214</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>29226</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>19572</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>44165</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>42,74%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>28,62%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>64,58%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>26658</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>19990</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>33517</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>39,33%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>29,49%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>49,44%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32557</t>
+          <t>27151</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22182</t>
+          <t>19984</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50791</t>
+          <t>34749</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>59215</t>
+          <t>56377</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46191</t>
+          <t>44391</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80724</t>
+          <t>72715</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>53,15%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>39158</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>24219</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>48812</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>57,26%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>35,42%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>71,38%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>41129</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>34270</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>47797</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>60,67%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>50,56%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>70,51%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>41312</t>
+          <t>41273</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23078</t>
+          <t>33675</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51687</t>
+          <t>48440</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>82442</t>
+          <t>80431</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>60933</t>
+          <t>64093</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>95466</t>
+          <t>92417</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,55%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>68384</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>68384</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>68384</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>67787</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>67787</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>67787</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>73869</t>
+          <t>68424</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>73869</t>
+          <t>68424</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73869</t>
+          <t>68424</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>141657</t>
+          <t>136808</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>141657</t>
+          <t>136808</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>141657</t>
+          <t>136808</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>22465</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>17241</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>26861</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>56,76%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>43,56%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>67,87%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>20208</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>15961</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>24499</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>59,09%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>46,67%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>71,63%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>23618</t>
+          <t>21070</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18385</t>
+          <t>16531</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28195</t>
+          <t>25340</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>43825</t>
+          <t>43536</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37245</t>
+          <t>36572</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49838</t>
+          <t>49407</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>65,92%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>17114</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>12718</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>22338</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>43,24%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>32,13%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>56,44%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>13992</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>9701</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>18239</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>40,91%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28,37%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>53,33%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17101</t>
+          <t>14300</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12524</t>
+          <t>10030</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22334</t>
+          <t>18839</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>31094</t>
+          <t>31413</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25081</t>
+          <t>25542</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37674</t>
+          <t>38377</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>51,2%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>39914</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>34396</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>43018</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>84,55%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>72,86%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>91,12%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>33763</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>28951</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>37150</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>78,9%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>67,66%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>86,82%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>45135</t>
+          <t>33948</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37731</t>
+          <t>29290</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48760</t>
+          <t>37562</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>78898</t>
+          <t>73862</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>70971</t>
+          <t>66463</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>83859</t>
+          <t>78886</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>87,66%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7295</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4191</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>12813</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>15,45%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>8,88%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>27,14%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>9026</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>5639</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>13838</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>21,1%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>13,18%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>32,34%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8647</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>13490</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>17673</t>
+          <t>16127</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12712</t>
+          <t>11103</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25600</t>
+          <t>23526</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,14%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>42789</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>42789</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>42789</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>42780</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>42780</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>42780</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>96571</t>
+          <t>89989</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>96571</t>
+          <t>89989</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>96571</t>
+          <t>89989</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>90626</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>80036</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>101050</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>64,66%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>57,1%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>72,09%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>75331</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>65693</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>84725</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>61,84%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>53,93%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>69,55%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>99036</t>
+          <t>75445</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>83557</t>
+          <t>67124</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>110594</t>
+          <t>85047</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>174367</t>
+          <t>166072</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>156429</t>
+          <t>152057</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>189046</t>
+          <t>181223</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>69,72%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>49538</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>39114</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>60128</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>35,34%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>27,91%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>42,9%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>46484</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>37090</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>56122</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>38,16%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>30,45%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>46,07%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>55544</t>
+          <t>44333</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>43986</t>
+          <t>34731</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>71023</t>
+          <t>52654</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>102028</t>
+          <t>93871</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>87349</t>
+          <t>78720</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>119966</t>
+          <t>107886</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>41,5%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140164</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140164</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140164</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>121815</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>121815</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>121815</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>154580</t>
+          <t>119778</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>154580</t>
+          <t>119778</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>154580</t>
+          <t>119778</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>276395</t>
+          <t>259943</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>276395</t>
+          <t>259943</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>276395</t>
+          <t>259943</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>64306</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>53207</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>75718</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>41,05%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>33,97%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>48,34%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>54229</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>45587</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>64261</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>42,54%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>35,76%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>50,41%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>62407</t>
+          <t>58220</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>51726</t>
+          <t>48430</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>73541</t>
+          <t>69242</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>116637</t>
+          <t>122526</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>103534</t>
+          <t>108436</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>132392</t>
+          <t>137871</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,11%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>92336</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>80924</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>103435</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>58,95%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>51,66%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>66,03%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>73239</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>63207</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>81881</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>57,46%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>49,59%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>64,24%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>91457</t>
+          <t>77786</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>80323</t>
+          <t>66764</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>102138</t>
+          <t>87576</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>164695</t>
+          <t>170122</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>148940</t>
+          <t>154777</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>177798</t>
+          <t>184212</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>62,95%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>156642</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>156642</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>156642</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>127468</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>127468</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>127468</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>153864</t>
+          <t>136006</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>153864</t>
+          <t>136006</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>153864</t>
+          <t>136006</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>281332</t>
+          <t>292648</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>281332</t>
+          <t>292648</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>281332</t>
+          <t>292648</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>343094</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>318777</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>369021</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>50,36%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>46,79%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>54,16%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>448</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>307072</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>286377</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>329456</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>49,64%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>46,3%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>53,26%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>376082</t>
+          <t>299151</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>348861</t>
+          <t>278773</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>404445</t>
+          <t>321070</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>683154</t>
+          <t>642245</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>646341</t>
+          <t>610007</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>719224</t>
+          <t>672454</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,2%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>457</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>338247</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>312320</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>362564</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>49,64%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>45,84%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>53,21%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>458</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>311493</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>289109</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>332188</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>50,36%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>46,74%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>53,7%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>457</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>362962</t>
+          <t>307626</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>334599</t>
+          <t>285707</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>390183</t>
+          <t>328004</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>674455</t>
+          <t>645872</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>638385</t>
+          <t>615663</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>711268</t>
+          <t>678110</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,64%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>932</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>681341</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>681341</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>681341</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>906</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>618565</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>618565</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>618565</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>932</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>739044</t>
+          <t>606777</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>739044</t>
+          <t>606777</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>739044</t>
+          <t>606777</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1357609</t>
+          <t>1288117</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1357609</t>
+          <t>1288117</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1357609</t>
+          <t>1288117</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
